--- a/autoIt/ImportFiles/ItemImportFromExcel.xlsx
+++ b/autoIt/ImportFiles/ItemImportFromExcel.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rakesh\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
     <sheet name="LanguageInfo" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="62">
   <si>
     <t>Item</t>
   </si>
@@ -28,54 +36,54 @@
     <t>General</t>
   </si>
   <si>
+    <t>sName</t>
+  </si>
+  <si>
+    <t>sCode</t>
+  </si>
+  <si>
+    <t>iProductType</t>
+  </si>
+  <si>
+    <t>fReorderLevel</t>
+  </si>
+  <si>
+    <t>iBinCapacity</t>
+  </si>
+  <si>
+    <t>iValuationMethod</t>
+  </si>
+  <si>
+    <t>bGroup</t>
+  </si>
+  <si>
+    <t>iParentId</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
-    <t>sName</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
-    <t>sCode</t>
-  </si>
-  <si>
     <t>Item Type</t>
   </si>
   <si>
-    <t>iProductType</t>
-  </si>
-  <si>
     <t>Reorder Level</t>
   </si>
   <si>
-    <t>fReorderLevel</t>
-  </si>
-  <si>
     <t>Bin capacity</t>
   </si>
   <si>
-    <t>iBinCapacity</t>
-  </si>
-  <si>
     <t>Valuation Method</t>
   </si>
   <si>
-    <t>iValuationMethod</t>
-  </si>
-  <si>
     <t>Group</t>
   </si>
   <si>
-    <t>bGroup</t>
-  </si>
-  <si>
     <t>Parent Code</t>
   </si>
   <si>
-    <t>iParentId</t>
-  </si>
-  <si>
     <t>ITEMS GROUP</t>
   </si>
   <si>
@@ -85,9 +93,6 @@
     <t>0.00</t>
   </si>
   <si>
-    <t>1.00</t>
-  </si>
-  <si>
     <t>Weighted Avg</t>
   </si>
   <si>
@@ -190,6 +195,9 @@
     <t>Standard</t>
   </si>
   <si>
+    <t>Item Import</t>
+  </si>
+  <si>
     <t>Language</t>
   </si>
   <si>
@@ -206,53 +214,199 @@
   </si>
   <si>
     <t>ITEM GROUP</t>
-  </si>
-  <si>
-    <t>Item Import</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color indexed="17"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color indexed="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="9"/>
-      <name val="Calibri"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color indexed="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="9"/>
-      <name val="Calibri"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,15 +416,203 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="17"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -287,47 +629,324 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -376,7 +995,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -411,7 +1030,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -585,152 +1204,90 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AX24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="23" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="25" customWidth="1" collapsed="1"/>
-    <col min="4" max="5" width="9" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="25" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="10" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="5" customWidth="1" collapsed="1"/>
-    <col min="9" max="10" width="25" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="10" customWidth="1" collapsed="1"/>
+    <col min="1" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="10" width="25" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="39.95" customHeight="1" spans="1:1">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
-      <c r="AM1" s="6"/>
-      <c r="AN1" s="6"/>
-      <c r="AO1" s="6"/>
-      <c r="AP1" s="6"/>
-      <c r="AQ1" s="6"/>
-      <c r="AR1" s="6"/>
-      <c r="AS1" s="6"/>
-      <c r="AT1" s="6"/>
-      <c r="AU1" s="6"/>
-      <c r="AV1" s="6"/>
-      <c r="AW1" s="6"/>
-      <c r="AX1" s="6"/>
-    </row>
-    <row r="2" spans="1:50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:1">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" spans="1:50" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" hidden="1" customHeight="1" spans="1:8">
       <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H3" t="s">
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="20.1" customHeight="1" spans="1:7">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -743,140 +1300,140 @@
       <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
         <v>21</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="G5" t="s">
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="1:8">
+      <c r="A6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
         <v>21</v>
       </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="20.1" customHeight="1" spans="1:7">
       <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
         <v>21</v>
       </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
       <c r="G7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="1:7">
       <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
         <v>21</v>
       </c>
-      <c r="F8" t="s">
-        <v>22</v>
-      </c>
       <c r="G8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="1:7">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
-        <v>21</v>
+      <c r="E9" s="5">
+        <v>1</v>
       </c>
       <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="1:7">
+      <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
         <v>21</v>
       </c>
-      <c r="F10" t="s">
-        <v>22</v>
-      </c>
       <c r="G10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="1:7">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -884,45 +1441,45 @@
       <c r="D11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
-        <v>21</v>
+      <c r="E11" s="5">
+        <v>1</v>
       </c>
       <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="1:7">
+      <c r="A12" t="s">
         <v>36</v>
       </c>
-      <c r="G11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" t="s">
-        <v>21</v>
+      <c r="E12" s="5">
+        <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="1:7">
       <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
         <v>39</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -930,22 +1487,22 @@
       <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
         <v>21</v>
       </c>
-      <c r="F13" t="s">
-        <v>22</v>
-      </c>
       <c r="G13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="1:7">
       <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
         <v>41</v>
-      </c>
-      <c r="B14" t="s">
-        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -953,22 +1510,22 @@
       <c r="D14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
         <v>21</v>
       </c>
-      <c r="F14" t="s">
-        <v>22</v>
-      </c>
       <c r="G14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="1:7">
       <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
         <v>43</v>
-      </c>
-      <c r="B15" t="s">
-        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -976,22 +1533,22 @@
       <c r="D15" t="s">
         <v>20</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
         <v>21</v>
       </c>
-      <c r="F15" t="s">
-        <v>22</v>
-      </c>
       <c r="G15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="1:7">
       <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
         <v>45</v>
-      </c>
-      <c r="B16" t="s">
-        <v>46</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -999,22 +1556,22 @@
       <c r="D16" t="s">
         <v>20</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
         <v>21</v>
       </c>
-      <c r="F16" t="s">
-        <v>22</v>
-      </c>
       <c r="G16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" spans="1:8">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
         <v>19</v>
@@ -1022,175 +1579,175 @@
       <c r="D17" t="s">
         <v>20</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
         <v>21</v>
       </c>
-      <c r="F17" t="s">
-        <v>22</v>
-      </c>
       <c r="G17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="20.1" customHeight="1" spans="1:7">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
         <v>20</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="5">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
         <v>21</v>
       </c>
-      <c r="F18" t="s">
-        <v>22</v>
-      </c>
       <c r="G18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="1:7">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
         <v>20</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="5">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
         <v>21</v>
       </c>
-      <c r="F19" t="s">
-        <v>22</v>
-      </c>
       <c r="G19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="1:7">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
         <v>20</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="5">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
         <v>21</v>
       </c>
-      <c r="F20" t="s">
-        <v>22</v>
-      </c>
       <c r="G20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" spans="1:7">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
         <v>20</v>
       </c>
-      <c r="E21" t="s">
-        <v>21</v>
+      <c r="E21" s="5">
+        <v>1</v>
       </c>
       <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="1:7">
+      <c r="A22" t="s">
         <v>52</v>
       </c>
-      <c r="G21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>53</v>
-      </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
         <v>20</v>
       </c>
-      <c r="E22" t="s">
-        <v>21</v>
+      <c r="E22" s="5">
+        <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="1:7">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
-      <c r="E23" t="s">
-        <v>21</v>
+      <c r="E23" s="5">
+        <v>1</v>
       </c>
       <c r="F23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
         <v>55</v>
       </c>
-      <c r="G23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>62</v>
-      </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>21</v>
+      <c r="E24" s="5">
+        <v>0.04</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G24" t="b">
         <v>0</v>
@@ -1203,28 +1760,27 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:C42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <sheetData>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row r="2" ht="24" customHeight="1" spans="1:1">
+      <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" hidden="1" customHeight="1" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -1233,9 +1789,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
+    <row r="4" ht="18" customHeight="1" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
@@ -1244,7 +1800,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="18" customHeight="1" spans="1:3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1255,205 +1811,205 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="18" customHeight="1" spans="1:3">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:3">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:3">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
         <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:3">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
       </c>
       <c r="C10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:3">
+      <c r="A11" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>35</v>
       </c>
       <c r="B11" t="s">
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:3">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
         <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:3">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
         <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:3">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
         <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:3">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
         <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:3">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:3">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
         <v>59</v>
       </c>
       <c r="C17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:3">
+      <c r="A18" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>48</v>
       </c>
       <c r="B18" t="s">
         <v>59</v>
       </c>
       <c r="C18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:3">
+      <c r="A19" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>49</v>
       </c>
       <c r="B19" t="s">
         <v>59</v>
       </c>
       <c r="C19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:3">
+      <c r="A20" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>50</v>
       </c>
       <c r="B20" t="s">
         <v>59</v>
       </c>
       <c r="C20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:3">
+      <c r="A21" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>51</v>
       </c>
       <c r="B21" t="s">
         <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:3">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
         <v>59</v>
       </c>
       <c r="C22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:3">
+      <c r="A23" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>54</v>
       </c>
       <c r="B23" t="s">
         <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -1464,202 +2020,202 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="18" customHeight="1" spans="1:3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:3">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
         <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:3">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
         <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:3">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
         <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:3">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
         <v>60</v>
       </c>
       <c r="C29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:3">
+      <c r="A30" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>35</v>
       </c>
       <c r="B30" t="s">
         <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:3">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
         <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:3">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
         <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:3">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
         <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:3">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
         <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:3">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
         <v>60</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:3">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
         <v>60</v>
       </c>
       <c r="C36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:3">
+      <c r="A37" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>48</v>
       </c>
       <c r="B37" t="s">
         <v>60</v>
       </c>
       <c r="C37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:3">
+      <c r="A38" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>49</v>
       </c>
       <c r="B38" t="s">
         <v>60</v>
       </c>
       <c r="C38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:3">
+      <c r="A39" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>50</v>
       </c>
       <c r="B39" t="s">
         <v>60</v>
       </c>
       <c r="C39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:3">
+      <c r="A40" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>51</v>
       </c>
       <c r="B40" t="s">
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:3">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
         <v>60</v>
       </c>
       <c r="C41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1" spans="1:3">
+      <c r="A42" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>54</v>
       </c>
       <c r="B42" t="s">
         <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1668,6 +2224,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>